--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121335154</v>
+        <v>121335149</v>
       </c>
       <c r="B2" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630336</v>
+        <v>630432</v>
       </c>
       <c r="R2" t="n">
-        <v>6725456</v>
+        <v>6725435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,12 +788,7 @@
         <v>121335150</v>
       </c>
       <c r="B3" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,6 +888,996 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121335151</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630382</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6725448</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121335152</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630377</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6725449</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121335153</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630367</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6725450</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121335154</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>630336</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6725456</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121335155</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630335</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6725457</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121335156</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630326</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6725461</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121335157</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630244</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6725475</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121335158</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>630214</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6725482</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121335159</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630216</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6725478</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>JPN0076 Najaderna</t>
         </is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335149</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335150</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335152</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335153</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335154</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335155</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335156</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335157</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335158</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,8 +1937,26 @@
           <t>JPN0076 Najaderna</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>